--- a/public/reporte_lcompra.xlsx
+++ b/public/reporte_lcompra.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46">
   <si>
     <t>#</t>
   </si>
@@ -41,34 +41,118 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>CASAMIA COMODIDAD PARA TU VIDA E.I.R.L</t>
-  </si>
-  <si>
-    <t>2025-07-05</t>
-  </si>
-  <si>
-    <t>BAZAN CHAVARRY JULIO ANDRES</t>
-  </si>
-  <si>
-    <t>2025-07-23</t>
-  </si>
-  <si>
-    <t>SODIMAC TIENDAS DEL MEJORAMIENTO DEL HOGAR S.A.</t>
-  </si>
-  <si>
-    <t>LACHUMA RODRIGUEZ LEANDRO "LACER COMERCIAL"</t>
-  </si>
-  <si>
-    <t>COMERCIO FERRETERO MUÑOZ S.R.L.</t>
-  </si>
-  <si>
-    <t>CONSORCIO E INVERSIONES PLASTILOPEZ S.A.C.</t>
-  </si>
-  <si>
-    <t>Compra de</t>
+    <t>COD CTA F</t>
+  </si>
+  <si>
+    <t>CUENTAFACT</t>
+  </si>
+  <si>
+    <t>COD CTA B</t>
+  </si>
+  <si>
+    <t>CUENTABASE</t>
+  </si>
+  <si>
+    <t>2025-10-10</t>
+  </si>
+  <si>
+    <t>DANIEL IZQUIERDO RUDAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIEZMO DEL MES </t>
+  </si>
+  <si>
+    <t>Facturas, boletas y otros comprobantes por cobrar</t>
+  </si>
+  <si>
+    <t>Diezmo actual</t>
+  </si>
+  <si>
+    <t>POR DIEZMOS Y OFRENDAS</t>
+  </si>
+  <si>
+    <t>2025-10-24</t>
+  </si>
+  <si>
+    <t>KEVIN ENRIQUE LOYOLA MERCADO</t>
+  </si>
+  <si>
+    <t>APORTE P COMPRA TECLADO</t>
+  </si>
+  <si>
+    <t>ALIPIO ANTONIO AVILA VALENCIA</t>
+  </si>
+  <si>
+    <t>ALBERTO ELEUTERIO ORTIZ CRUZ</t>
+  </si>
+  <si>
+    <t>OFRENDA LIBRE</t>
+  </si>
+  <si>
+    <t>JULIO RUBEN RAMIREZ PABLO</t>
+  </si>
+  <si>
+    <t>JESUS MANUEL GUTIERREZ ARENAS</t>
+  </si>
+  <si>
+    <t>JORGE ALBERTO GARCIA JUAREZ</t>
+  </si>
+  <si>
+    <t>JONATHAN RUBEN RAMIREZ SANGAY</t>
+  </si>
+  <si>
+    <t>JAIME LUIS CORCUERA UCEDA</t>
+  </si>
+  <si>
+    <t>JUANA BERTHA JUAREZ DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>EVELYN MARGARITA MEZA RUIZ</t>
+  </si>
+  <si>
+    <t>2025-10-30</t>
+  </si>
+  <si>
+    <t>SEGUNDO JULIO CHUSHO VARGAS</t>
+  </si>
+  <si>
+    <t>DIEZMO Y OFRENDA</t>
+  </si>
+  <si>
+    <t>OFRENDA MISIONES 29OCT202525</t>
+  </si>
+  <si>
+    <t>LEYVER NELSON MUDARRA SANDOVAL</t>
+  </si>
+  <si>
+    <t>DIEZMOS Y OFRENDAS</t>
+  </si>
+  <si>
+    <t>ALBERTO IZQUIERDO RUDAS</t>
+  </si>
+  <si>
+    <t>DIEZMOS Y OFRENDAS 5 MESES</t>
+  </si>
+  <si>
+    <t>MISIONES, DIEZMO Y OFRENDA</t>
+  </si>
+  <si>
+    <t>DIEZMO Y OFRENDA R.LIBERTAD SET-25</t>
+  </si>
+  <si>
+    <t>DIEZMOS Y OFRENDAS MISIONES 31OCT2025</t>
+  </si>
+  <si>
+    <t>2025-10-31</t>
+  </si>
+  <si>
+    <t>DIEZMO AGOSTO1-REGION</t>
+  </si>
+  <si>
+    <t>DIEZMO OFRENDA OCTUBRE 25 REGION</t>
+  </si>
+  <si>
+    <t>DIEZMO AGOSTO 2 - REGION</t>
   </si>
 </sst>
 </file>
@@ -408,21 +492,24 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="2.285" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="3.428" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="56.558" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="36.42" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="44.703" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="22.28" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="4.57" bestFit="true" customWidth="true" style="0"/>
     <col min="8" max="8" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="9.10" bestFit="true" style="0"/>
+    <col min="9" max="9" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="58.843" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="16.425" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -447,146 +534,929 @@
       <c r="H2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>20612951862</v>
+        <v>18838574</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>2478.80999999999995</v>
+        <v>20.0</v>
       </c>
       <c r="G3">
-        <v>446.19</v>
+        <v>0.0</v>
       </c>
       <c r="H3">
-        <v>2925.0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>20.0</v>
+      </c>
+      <c r="I3">
+        <v>121</v>
+      </c>
+      <c r="J3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3">
+        <v>751</v>
+      </c>
+      <c r="L3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>10179822950</v>
+        <v>18838574</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>127.12</v>
+        <v>18.0</v>
       </c>
       <c r="G4">
-        <v>22.88</v>
+        <v>0.0</v>
       </c>
       <c r="H4">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>18.0</v>
+      </c>
+      <c r="I4">
+        <v>121</v>
+      </c>
+      <c r="J4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4">
+        <v>751</v>
+      </c>
+      <c r="L4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C5">
-        <v>20112273922</v>
+        <v>47329849</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>119.31999999999999</v>
+        <v>500.0</v>
       </c>
       <c r="G5">
-        <v>21.48</v>
+        <v>0.0</v>
       </c>
       <c r="H5">
-        <v>140.80000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>500.0</v>
+      </c>
+      <c r="I5">
+        <v>121</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <v>751</v>
+      </c>
+      <c r="L5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C6">
-        <v>10408389980</v>
+        <v>18861304</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>95.76000000000001</v>
+        <v>250.0</v>
       </c>
       <c r="G6">
-        <v>17.24</v>
+        <v>0.0</v>
       </c>
       <c r="H6">
-        <v>113.0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>250.0</v>
+      </c>
+      <c r="I6">
+        <v>121</v>
+      </c>
+      <c r="J6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6">
+        <v>751</v>
+      </c>
+      <c r="L6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C7">
-        <v>20612254550</v>
+        <v>18898317</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>91.099999999999994</v>
+        <v>500.0</v>
       </c>
       <c r="G7">
-        <v>16.4</v>
+        <v>0.0</v>
       </c>
       <c r="H7">
-        <v>107.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>500.0</v>
+      </c>
+      <c r="I7">
+        <v>121</v>
+      </c>
+      <c r="J7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>751</v>
+      </c>
+      <c r="L7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8">
+        <v>99999999</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8">
+        <v>480.0</v>
+      </c>
+      <c r="G8">
+        <v>0.0</v>
+      </c>
+      <c r="H8">
+        <v>480.0</v>
+      </c>
+      <c r="I8">
+        <v>121</v>
+      </c>
+      <c r="J8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>751</v>
+      </c>
+      <c r="L8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9">
+        <v>99999999</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9">
+        <v>500.0</v>
+      </c>
+      <c r="G9">
+        <v>0.0</v>
+      </c>
+      <c r="H9">
+        <v>500.0</v>
+      </c>
+      <c r="I9">
+        <v>121</v>
+      </c>
+      <c r="J9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9">
+        <v>751</v>
+      </c>
+      <c r="L9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>42231190</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10">
+        <v>500.0</v>
+      </c>
+      <c r="G10">
+        <v>0.0</v>
+      </c>
+      <c r="H10">
+        <v>500.0</v>
+      </c>
+      <c r="I10">
+        <v>121</v>
+      </c>
+      <c r="J10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10">
+        <v>751</v>
+      </c>
+      <c r="L10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11">
+        <v>70652190</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11">
+        <v>500.0</v>
+      </c>
+      <c r="G11">
+        <v>0.0</v>
+      </c>
+      <c r="H11">
+        <v>500.0</v>
+      </c>
+      <c r="I11">
+        <v>121</v>
+      </c>
+      <c r="J11" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11">
+        <v>751</v>
+      </c>
+      <c r="L11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12">
+        <v>18837961</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12">
+        <v>500.0</v>
+      </c>
+      <c r="G12">
+        <v>0.0</v>
+      </c>
+      <c r="H12">
+        <v>500.0</v>
+      </c>
+      <c r="I12">
+        <v>121</v>
+      </c>
+      <c r="J12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12">
+        <v>751</v>
+      </c>
+      <c r="L12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>76083131</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13">
+        <v>500.0</v>
+      </c>
+      <c r="G13">
+        <v>0.0</v>
+      </c>
+      <c r="H13">
+        <v>500.0</v>
+      </c>
+      <c r="I13">
+        <v>121</v>
+      </c>
+      <c r="J13" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13">
+        <v>751</v>
+      </c>
+      <c r="L13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14">
         <v>12</v>
       </c>
-      <c r="C8">
-        <v>20440422072</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14">
+        <v>18848453</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14">
+        <v>250.0</v>
+      </c>
+      <c r="G14">
+        <v>0.0</v>
+      </c>
+      <c r="H14">
+        <v>250.0</v>
+      </c>
+      <c r="I14">
+        <v>121</v>
+      </c>
+      <c r="J14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14">
+        <v>751</v>
+      </c>
+      <c r="L14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15">
+        <v>18837971</v>
+      </c>
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15">
+        <v>500.0</v>
+      </c>
+      <c r="G15">
+        <v>0.0</v>
+      </c>
+      <c r="H15">
+        <v>500.0</v>
+      </c>
+      <c r="I15">
+        <v>121</v>
+      </c>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15">
+        <v>751</v>
+      </c>
+      <c r="L15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16">
+        <v>75495571</v>
+      </c>
+      <c r="D16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16">
+        <v>500.0</v>
+      </c>
+      <c r="G16">
+        <v>0.0</v>
+      </c>
+      <c r="H16">
+        <v>500.0</v>
+      </c>
+      <c r="I16">
+        <v>121</v>
+      </c>
+      <c r="J16" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16">
+        <v>751</v>
+      </c>
+      <c r="L16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17">
+        <v>40440582</v>
+      </c>
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17">
+        <v>100.0</v>
+      </c>
+      <c r="G17">
+        <v>0.0</v>
+      </c>
+      <c r="H17">
+        <v>100.0</v>
+      </c>
+      <c r="I17">
+        <v>121</v>
+      </c>
+      <c r="J17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17">
+        <v>751</v>
+      </c>
+      <c r="L17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18">
+        <v>99999999</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18">
+        <v>600.0</v>
+      </c>
+      <c r="G18">
+        <v>0.0</v>
+      </c>
+      <c r="H18">
+        <v>600.0</v>
+      </c>
+      <c r="I18">
+        <v>121</v>
+      </c>
+      <c r="J18" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18">
+        <v>751</v>
+      </c>
+      <c r="L18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19">
         <v>17</v>
       </c>
-      <c r="F8">
-        <v>103.56</v>
-      </c>
-      <c r="G8">
-        <v>18.64</v>
-      </c>
-      <c r="H8">
-        <v>122.2</v>
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19">
+        <v>44652136</v>
+      </c>
+      <c r="D19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19">
+        <v>100.0</v>
+      </c>
+      <c r="G19">
+        <v>0.0</v>
+      </c>
+      <c r="H19">
+        <v>100.0</v>
+      </c>
+      <c r="I19">
+        <v>121</v>
+      </c>
+      <c r="J19" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19">
+        <v>751</v>
+      </c>
+      <c r="L19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20">
+        <v>18859788</v>
+      </c>
+      <c r="D20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20">
+        <v>400.0</v>
+      </c>
+      <c r="G20">
+        <v>0.0</v>
+      </c>
+      <c r="H20">
+        <v>400.0</v>
+      </c>
+      <c r="I20">
+        <v>121</v>
+      </c>
+      <c r="J20" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20">
+        <v>751</v>
+      </c>
+      <c r="L20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21">
+        <v>99999999</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21">
+        <v>700.0</v>
+      </c>
+      <c r="G21">
+        <v>0.0</v>
+      </c>
+      <c r="H21">
+        <v>700.0</v>
+      </c>
+      <c r="I21">
+        <v>121</v>
+      </c>
+      <c r="J21" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21">
+        <v>751</v>
+      </c>
+      <c r="L21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22">
+        <v>99999999</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22">
+        <v>606.10000000000002</v>
+      </c>
+      <c r="G22">
+        <v>0.0</v>
+      </c>
+      <c r="H22">
+        <v>606.10000000000002</v>
+      </c>
+      <c r="I22">
+        <v>121</v>
+      </c>
+      <c r="J22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22">
+        <v>751</v>
+      </c>
+      <c r="L22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23">
+        <v>99999999</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23">
+        <v>590.20000000000005</v>
+      </c>
+      <c r="G23">
+        <v>0.0</v>
+      </c>
+      <c r="H23">
+        <v>590.20000000000005</v>
+      </c>
+      <c r="I23">
+        <v>121</v>
+      </c>
+      <c r="J23" t="s">
+        <v>15</v>
+      </c>
+      <c r="K23">
+        <v>751</v>
+      </c>
+      <c r="L23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24">
+        <v>99999999</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24">
+        <v>600.0</v>
+      </c>
+      <c r="G24">
+        <v>0.0</v>
+      </c>
+      <c r="H24">
+        <v>600.0</v>
+      </c>
+      <c r="I24">
+        <v>121</v>
+      </c>
+      <c r="J24" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24">
+        <v>751</v>
+      </c>
+      <c r="L24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25">
+        <v>99999999</v>
+      </c>
+      <c r="D25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" t="s">
+        <v>44</v>
+      </c>
+      <c r="F25">
+        <v>635.79999999999995</v>
+      </c>
+      <c r="G25">
+        <v>0.0</v>
+      </c>
+      <c r="H25">
+        <v>635.79999999999995</v>
+      </c>
+      <c r="I25">
+        <v>121</v>
+      </c>
+      <c r="J25" t="s">
+        <v>15</v>
+      </c>
+      <c r="K25">
+        <v>751</v>
+      </c>
+      <c r="L25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26">
+        <v>99999999</v>
+      </c>
+      <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26">
+        <v>657.39999999999998</v>
+      </c>
+      <c r="G26">
+        <v>0.0</v>
+      </c>
+      <c r="H26">
+        <v>657.39999999999998</v>
+      </c>
+      <c r="I26">
+        <v>121</v>
+      </c>
+      <c r="J26" t="s">
+        <v>15</v>
+      </c>
+      <c r="K26">
+        <v>751</v>
+      </c>
+      <c r="L26" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
